--- a/原始数据/新质生产力测度指标/行政区划.xlsx
+++ b/原始数据/新质生产力测度指标/行政区划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\31743\Documents\GitHub\tjjmlinxieli\原始数据\新质生产力测度指标\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB38D6A2-F8E1-4DAC-9F53-289E12113A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DE4BA2-F30E-45E3-AC0A-C4C764660F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="15196" xr2:uid="{DC516169-A7DB-4BF7-9BB0-CE49883DD7D6}"/>
   </bookViews>
